--- a/tests/workbooktests/workbooks/test_instruments.xlsx
+++ b/tests/workbooktests/workbooks/test_instruments.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sebastian\01_GitHub\sschlenkrich\QuantLibXlOil\tests\workbooks\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sebastian\01_GitHub\sschlenkrich\QuantLibXlOil\tests\workbooktests\workbooks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E6DAFE7F-8155-4659-93A9-3B2076244471}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E399980-9858-4CCA-BBF3-2A65C90830E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6630" yWindow="-20745" windowWidth="21330" windowHeight="15900" xr2:uid="{BCB1E234-DE95-429A-B79F-DDE7EC2282D0}"/>
+    <workbookView xWindow="3450" yWindow="-18675" windowWidth="30690" windowHeight="16530" xr2:uid="{BCB1E234-DE95-429A-B79F-DDE7EC2282D0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -500,7 +500,7 @@
       </c>
       <c r="B6" t="str" cm="1">
         <f t="array" ref="B6">_xll.qlStock(B2)</f>
-        <v>⚡[Book1]Sheet1!R6C2Stock,A</v>
+        <v>欣[test_instruments.xlsx]Sheet1!R6C2Stock,A</v>
       </c>
       <c r="C6" cm="1">
         <f t="array" ref="C6">_xll.qlInstrumentNPV(B6)</f>
@@ -513,7 +513,7 @@
       </c>
       <c r="B7" t="str" cm="1">
         <f t="array" ref="B7">_xll.qlStock(B3)</f>
-        <v>⚡[Book1]Sheet1!R7C2Stock,A</v>
+        <v>欣[test_instruments.xlsx]Sheet1!R7C2Stock,A</v>
       </c>
       <c r="C7" cm="1">
         <f t="array" ref="C7">_xll.qlInstrumentNPV(B7)</f>
@@ -526,7 +526,7 @@
       </c>
       <c r="B8" t="str" cm="1">
         <f t="array" ref="B8">_xll.qlStock(B4)</f>
-        <v>⚡[Book1]Sheet1!R8C2Stock,A</v>
+        <v>欣[test_instruments.xlsx]Sheet1!R8C2Stock,A</v>
       </c>
       <c r="C8" cm="1">
         <f t="array" ref="C8">_xll.qlInstrumentNPV(B8)</f>
@@ -547,7 +547,7 @@
       </c>
       <c r="B11" t="str" cm="1">
         <f t="array" ref="B11">_xll.qlCompositeInstrument(B6:B8)</f>
-        <v>⚡[Book1]Sheet1!R11C2CompositeInstrument,A</v>
+        <v>欣[test_instruments.xlsx]Sheet1!R11C2CompositeInstrument,A</v>
       </c>
       <c r="C11" cm="1">
         <f t="array" ref="C11">_xll.qlInstrumentNPV(B11)</f>
@@ -564,7 +564,7 @@
       </c>
       <c r="B12" t="str" cm="1">
         <f t="array" ref="B12">_xll.qlCompositeInstrument(B6:B8,C3)</f>
-        <v>⚡[Book1]Sheet1!R12C2CompositeInstrument,A</v>
+        <v>欣[test_instruments.xlsx]Sheet1!R12C2CompositeInstrument,A</v>
       </c>
       <c r="C12" cm="1">
         <f t="array" ref="C12">_xll.qlInstrumentNPV(B12)</f>
@@ -581,7 +581,7 @@
       </c>
       <c r="B13" t="str" cm="1">
         <f t="array" ref="B13">_xll.qlCompositeInstrument(B6:B8,C2:C4)</f>
-        <v>⚡[Book1]Sheet1!R13C2CompositeInstrument,A</v>
+        <v>欣[test_instruments.xlsx]Sheet1!R13C2CompositeInstrument,A</v>
       </c>
       <c r="C13" cm="1">
         <f t="array" ref="C13">_xll.qlInstrumentNPV(B13)</f>
